--- a/reference/origins/product info/WA_Drinks_50_Product_List_Source_Inspired_Unique_Descriptions.xlsx
+++ b/reference/origins/product info/WA_Drinks_50_Product_List_Source_Inspired_Unique_Descriptions.xlsx
@@ -2300,7 +2300,7 @@
     <row r="28" ht="34" customHeight="1" s="20">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Swifts</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N28" s="12" t="inlineStr">
         <is>
-          <t>Mock extension based on Swift's established product format/flavor direction</t>
+          <t>Mock extension based on Swifts' established product format/flavor direction</t>
         </is>
       </c>
       <c r="O28" s="12" t="n"/>
@@ -2365,7 +2365,7 @@
     <row r="29" ht="34" customHeight="1" s="20">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Swifts</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="N29" s="12" t="inlineStr">
         <is>
-          <t>Mock extension based on Swift's established product format/flavor direction</t>
+          <t>Mock extension based on Swifts' established product format/flavor direction</t>
         </is>
       </c>
       <c r="O29" s="12" t="n"/>
@@ -2430,7 +2430,7 @@
     <row r="30" ht="34" customHeight="1" s="20">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Swifts</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
-          <t>Mock extension based on Swift's established product format/flavor direction</t>
+          <t>Mock extension based on Swifts' established product format/flavor direction</t>
         </is>
       </c>
       <c r="O30" s="12" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="31" ht="34" customHeight="1" s="20">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Swifts</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
-          <t>Mock extension based on Swift's established product format/flavor direction</t>
+          <t>Mock extension based on Swifts' established product format/flavor direction</t>
         </is>
       </c>
       <c r="O31" s="12" t="n"/>
@@ -2564,7 +2564,7 @@
     <row r="32" ht="34" customHeight="1" s="20">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Swifts</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="N32" s="12" t="inlineStr">
         <is>
-          <t>Mock extension based on Swift's established product format/flavor direction</t>
+          <t>Mock extension based on Swifts' established product format/flavor direction</t>
         </is>
       </c>
       <c r="O32" s="12" t="n"/>
